--- a/INVENTAIRE_DES_MCF_ANTENNE_PEV_LUIZA_FEVRIER_2026_VF.xlsx
+++ b/INVENTAIRE_DES_MCF_ANTENNE_PEV_LUIZA_FEVRIER_2026_VF.xlsx
@@ -1139,6 +1139,150 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>1</rowOff>
+    </from>
+    <to>
+      <col>3</col>
+      <colOff>971550</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 25" descr="wps1"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="1"/>
+          <a:ext cx="6172200" cy="1466850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>1</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>971550</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 25" descr="wps1"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="1"/>
+          <a:ext cx="6172200" cy="1333499"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>247650</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>133350</colOff>
+      <row>6</row>
+      <rowOff>190499</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 25" descr="wps1"/>
+        <cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="247650" y="0"/>
+          <a:ext cx="6781800" cy="1333499"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -7140,6 +7284,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7895,6 +8040,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="68"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8271,5 +8417,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" scale="93"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>